--- a/backend/领星/导入领星/读取文件信息/产品汇总表-模版 .xlsx
+++ b/backend/领星/导入领星/读取文件信息/产品汇总表-模版 .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="产品汇总" sheetId="1" r:id="rId1"/>
@@ -383,12 +383,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -1006,19 +1006,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -1185,7 +1185,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1212,13 +1212,13 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1764,21 +1764,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AZ713"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="16.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.025" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.2166666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.0277777777778" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.212962962963" style="1" customWidth="1"/>
     <col min="6" max="14" width="9" style="1" customWidth="1"/>
     <col min="27" max="33" width="5" style="1" customWidth="1"/>
-    <col min="34" max="41" width="7.775" style="1" customWidth="1"/>
-    <col min="42" max="47" width="17.1333333333333" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.8" style="1" customWidth="1"/>
-    <col min="49" max="49" width="15.3583333333333" style="3" customWidth="1"/>
+    <col min="34" max="41" width="7.77777777777778" style="1" customWidth="1"/>
+    <col min="42" max="47" width="17.1296296296296" style="1" customWidth="1"/>
+    <col min="48" max="48" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="49" max="49" width="15.3611111111111" style="3" customWidth="1"/>
     <col min="50" max="51" width="9" style="1" customWidth="1"/>
     <col min="52" max="52" width="11.5" style="1" customWidth="1"/>
-    <col min="53" max="53" width="15.2" style="1" customWidth="1"/>
+    <col min="53" max="53" width="15.2037037037037" style="1" customWidth="1"/>
     <col min="54" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25126,7 +25126,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
